--- a/paper/tables/final/Tabela_1.xlsx
+++ b/paper/tables/final/Tabela_1.xlsx
@@ -704,7 +704,7 @@
     <t>13,25</t>
   </si>
   <si>
-    <t>Fonte: Mais Retorno (relatórios PDF exportados; licença comercial).</t>
+    <t>Fonte: Mais Retorno (relatórios PDF exportados; uso acadêmico autorizado).</t>
   </si>
   <si>
     <t>Nota: O retorno total é apresentado como multiplicador final (×). CAGR em % a.a. Este painel reporta o snapshot D-12m.</t>
